--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-001</t>
+          <t>TC-TU-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>本地上传_jpg_2MB</t>
+          <t>测试上传_正常jpg</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=2MB_jpg</t>
+          <t>POST /file/test/upload file=1MB_jpg</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, url 字段为可访问图片链接</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -603,7 +603,7 @@
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-002</t>
+          <t>TC-TU-002</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -626,22 +626,22 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>本地上传_png</t>
+          <t>测试上传_空文件</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=1MB_png</t>
+          <t>file=0byte</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -656,7 +656,7 @@
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-003</t>
+          <t>TC-TU-003</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -679,22 +679,22 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>本地上传_avatar_头像</t>
+          <t>测试上传_非图片</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=512KB_jpg</t>
+          <t>file=test.pdf</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, userAvatar 已更新</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-004</t>
+          <t>TC-FU-001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -728,26 +728,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>本地上传_超过2MB_应失败</t>
+          <t>上传_正常png</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload file=5MB_jpg</t>
+          <t>POST /file/upload file=1MB_png</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -762,7 +762,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-FL-005</t>
+          <t>TC-FU-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -781,26 +781,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>本地上传_未登录</t>
+          <t>上传_超过2MB</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload</t>
+          <t>file=5MB_jpg</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-001</t>
+          <t>TC-FU-003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/文件上传</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -838,22 +838,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>门户_GET_签名验证</t>
+          <t>上传_未登录</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>微信服务器 GET</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. GET /wx/mp/portal signature=xxx timestamp=xxx nonce=xxx echostr=xxx</t>
+          <t>POST /file/upload</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>返回 echostr 明文（签名验证通过）</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-002</t>
+          <t>TC-AU-001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -891,23 +891,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>门户_POST_消息处理</t>
+          <t>头像_正常</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>微信服务器 POST XML</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/portal Content-Type=application/xml
-2. body=&lt;xml&gt;...&lt;/xml&gt;</t>
+          <t>POST /file/upload/avatar file=300KB_jpg</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, 响应 XML 包含正确结构</t>
+          <t>code=0, userAvatar更新</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -922,7 +921,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-003</t>
+          <t>TC-AU-002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -932,7 +931,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -941,26 +940,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>创建公众号菜单</t>
+          <t>头像_超过1MB</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/menu/create menu={"button":[...]}</t>
+          <t>file=1.5MB</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -975,7 +974,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-004</t>
+          <t>TC-AU-003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -985,7 +984,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -994,26 +993,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>门户_GET_签名错误</t>
+          <t>头像_非图片</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>伪造签名</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. GET /wx/mp/portal signature=invalid</t>
+          <t>file=test.pdf</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>返回空或失败提示</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1028,7 +1027,7 @@
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-WX-005</t>
+          <t>TC-WG-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1038,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/微信公众号</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1047,26 +1046,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>门户_POST_未登录</t>
+          <t>门户_GET_签名验证</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>微信GET</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. POST /wx/mp/portal</t>
+          <t>GET /wx/mp/portal signature=xxx timestamp=xxx nonce=xxx echostr=test</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100 或 40300</t>
+          <t>返回echostr</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1081,7 +1080,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-WG-002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1091,35 +1090,35 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>上传_50并发_1MB</t>
+          <t>门户_GET_签名错误</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>微信GET</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程上传 1MB jpg</t>
+          <t>signature=invalid</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 2s, 错误率 &lt; 5%</t>
+          <t>返回空或错误</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1134,7 +1133,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-WG-003</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1144,35 +1143,35 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>upload_缺multipart边界</t>
+          <t>门户_GET_缺参数</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>微信GET</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1. 发送不完整 multipart 请求</t>
+          <t>无signature参数</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回 400 或 415</t>
+          <t>返回错误</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1187,7 +1186,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-WP-001</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1197,12 +1196,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/文件上传</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1210,22 +1209,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>上传_双扩展名</t>
+          <t>门户_POST_正常文本</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>微信POST</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1. file=1.jpg.php</t>
+          <t>POST /wx/mp/portal body=&lt;xml&gt;...</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, 响应XML</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1240,7 +1239,7 @@
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-006</t>
+          <t>TC-WP-002</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1250,7 +1249,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1259,26 +1258,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>头像_超过1MB_应失败</t>
+          <t>门户_POST_空body</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>微信POST</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=1.5MB_jpg</t>
+          <t>body=空</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 超限</t>
+          <t>返回错误XML</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1293,7 +1292,7 @@
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-007</t>
+          <t>TC-WP-003</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1303,7 +1302,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/微信门户</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1312,26 +1311,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>头像_非图片文件_应失败</t>
+          <t>门户_POST_格式错误</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>微信POST</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=test.pdf</t>
+          <t>body=非XML</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>返回错误</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1346,7 +1345,7 @@
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-008</t>
+          <t>TC-MC-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1356,7 +1355,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/微信菜单</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1365,26 +1364,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>头像_webp格式</t>
+          <t>创建菜单_正常</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=300KB_webp</t>
+          <t>POST /wx/mp/menu/create menu={button:[...]}</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 picFormat=webp</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1399,7 +1398,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-009</t>
+          <t>TC-MC-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1409,7 +1408,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/微信菜单</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1418,26 +1417,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>头像_空文件_应失败</t>
+          <t>创建菜单_空body</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1. POST /file/upload/avatar file=0byte</t>
+          <t>body={}</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1452,7 +1451,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-AT-010</t>
+          <t>TC-MC-003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1462,7 +1461,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/头像上传</t>
+          <t>/微信菜单</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1471,27 +1470,26 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>头像_重复上传覆盖旧头像</t>
+          <t>创建菜单_未登录</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1. 先上传头像A
-2. 再上传头像B</t>
+          <t>POST /wx/mp/menu/create</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 userAvatar 改为新URL</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1506,7 +1504,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-006</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1516,35 +1514,35 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/文件上传</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>获取_管理员视角</t>
+          <t>上传_50并发1MB</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1. GET /user/get/login (admin Cookie)</t>
+          <t>50线程 POST /file/upload</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含 userRole=admin</t>
+          <t>P95&lt;2s</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1559,7 +1557,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-007</t>
+          <t>TC-PERF-002</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1569,12 +1567,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -1582,22 +1580,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>获取_id为字符串</t>
+          <t>头像_100并发</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1. Cookie伪造 userId='abc'</t>
+          <t>100线程 POST /file/upload/avatar</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>P95&lt;3s</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1612,7 +1610,7 @@
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-008</t>
+          <t>TC-API-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1622,35 +1620,35 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/文件上传</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>获取_用户信息完整</t>
+          <t>上传_缺multipart边界</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1. GET /user/get/login</t>
+          <t>不完整multipart</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含 userAvatar/userName/userProfile</t>
+          <t>400/415</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1665,7 +1663,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-009</t>
+          <t>TC-SEC-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1675,7 +1673,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/文件上传</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1688,22 +1686,22 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>XSS_用户简介</t>
+          <t>上传_伪PHP木马</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userProfile='&lt;script&gt;alert(1)&lt;/script&gt;'</t>
+          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 渲染时被转义</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1718,7 +1716,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-010</t>
+          <t>TC-SEC-002</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1728,12 +1726,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>/获取当前用户</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -1741,22 +1739,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>获取_用户简介含emoji</t>
+          <t>头像_双扩展名绕过</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userProfile='😀 用户'</t>
+          <t>file=1.jpg.php</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1771,7 +1769,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-001</t>
+          <t>TC-SEC-003</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1781,12 +1779,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/用户更新</t>
+          <t>/头像上传</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>功能测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
@@ -1794,22 +1792,22 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>更新_昵称</t>
+          <t>头像_越权修改别人</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>testuser02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/update/my userName='新名字'</t>
+          <t>POST /file/upload/avatar userId=别人</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>只改本人</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1821,220 +1819,8 @@
       </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="80" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TC-UU-002</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>/用户更新</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>更新_昵称为空</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>testuser01 已登录</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1. POST /user/update/my userName=''</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="80" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TC-UU-003</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>/用户更新</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>更新_缺userName</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>testuser01 已登录</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>1. body 无 userName</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>返回code=40001</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28" ht="80" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TC-PERF-002</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>头像上传_100并发</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>已安装 JMeter</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1. JMeter 100 线程 POST /file/upload/avatar</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>P95 &lt; 3s, 错误率 &lt; 5%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="80" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TC-SEC-002</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>头像_伪SVG含JS</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>testuser01 已登录</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>1. file=avatar.svg 内容含 &lt;script&gt;alert(1)&lt;/script&gt;</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>返回code=40001 拒绝SVG</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>林景彬</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M29"/>
+  <autoFilter ref="A1:M25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2071,13 +1857,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -2087,21 +1873,21 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2111,7 +1897,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
@@ -8,11 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$25</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,14 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,39 +54,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,25 +436,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>用例编号</t>
@@ -547,43 +521,44 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC-TU-001</t>
+          <t>TC-FT-001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>/file/test/upload</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>测试上传_正常jpg</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>test_upload_正常jpg</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>POST /file/test/upload file=1MB_jpg</t>
+          <t>POST /file/test/upload
+Body: multipart file=1MB_jpg</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -600,48 +575,49 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TC-TU-002</t>
+          <t>TC-FL-001</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>测试上传_空文件</t>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_正常jpg</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>file=0byte</t>
+          <t>POST /file/upload
+Body: multipart file=2MB_jpg</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -653,48 +629,49 @@
       </c>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC-TU-003</t>
+          <t>TC-FL-002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>测试上传_非图片</t>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_png</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>file=test.pdf</t>
+          <t>POST /file/upload
+Body: multipart file=1MB_png</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -706,48 +683,49 @@
       </c>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-FU-001</t>
+          <t>TC-FL-003</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>上传_正常png</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_超2MB</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>POST /file/upload file=1MB_png</t>
+          <t>POST /file/upload
+Body: multipart file=5MB_jpg</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -759,43 +737,44 @@
       </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-FU-002</t>
+          <t>TC-FL-004</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>上传_超过2MB</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_非图片</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>file=5MB_jpg</t>
+          <t>POST /file/upload
+Body: multipart file=test.pdf</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -812,48 +791,49 @@
       </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-FU-003</t>
+          <t>TC-FL-005</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>上传_未登录</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_空文件</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>POST /file/upload</t>
+          <t>POST /file/upload
+Body: multipart file=0byte.jpg</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -865,48 +845,49 @@
       </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-AU-001</t>
+          <t>TC-FL-006</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>头像_正常</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>上传_伪JSP木马</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>POST /file/upload/avatar file=300KB_jpg</t>
+          <t>POST /file/upload
+Body: multipart file=1.jpg (内容是 &lt;?php system($_GET['c']);?&gt;)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>code=0, userAvatar更新</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -918,43 +899,44 @@
       </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-AU-002</t>
+          <t>TC-FL-007</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>头像_超过1MB</t>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>上传_双扩展名绕过</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>file=1.5MB</t>
+          <t>POST /file/upload
+Body: multipart file=1.jpg.php</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -971,48 +953,49 @@
       </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-AU-003</t>
+          <t>TC-FL-008</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>头像_非图片</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>本地上传_未登录</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>file=test.pdf</t>
+          <t>POST /file/upload
+Body: multipart file=1MB_jpg</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1024,48 +1007,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-WG-001</t>
+          <t>TC-FA-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>门户_GET_签名验证</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>头像上传_jpg</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>微信GET</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>GET /wx/mp/portal signature=xxx timestamp=xxx nonce=xxx echostr=test</t>
+          <t>POST /file/upload/avatar
+Body: multipart file=512KB_jpg</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回echostr</t>
+          <t>code=0, userAvatar 已更新</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1077,48 +1061,49 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-WG-002</t>
+          <t>TC-FA-002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>门户_GET_签名错误</t>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>头像上传_png</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>微信GET</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>signature=invalid</t>
+          <t>POST /file/upload/avatar
+Body: multipart file=512KB_png</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>返回空或错误</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1130,48 +1115,49 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-WG-003</t>
+          <t>TC-FA-003</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>门户_GET_缺参数</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>头像上传_超2MB</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>微信GET</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>无signature参数</t>
+          <t>POST /file/upload/avatar
+Body: multipart file=5MB_jpg</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回错误</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1183,48 +1169,49 @@
       </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="80" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-WP-001</t>
+          <t>TC-FA-004</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>门户_POST_正常文本</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>头像上传_非图片</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>微信POST</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>POST /wx/mp/portal body=&lt;xml&gt;...</t>
+          <t>POST /file/upload/avatar
+Body: multipart file=test.pdf</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>code=0, 响应XML</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1236,48 +1223,49 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-WP-002</t>
+          <t>TC-FA-005</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>门户_POST_空body</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload/avatar</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>头像上传_空文件</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>微信POST</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>body=空</t>
+          <t>POST /file/upload/avatar
+Body: multipart file=0byte.jpg</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回错误XML</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1289,48 +1277,49 @@
       </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-WP-003</t>
+          <t>TC-GC-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>/微信门户</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>门户_POST_格式错误</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>获取当前用户_已登录</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>微信POST</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>body=非XML</t>
+          <t>GET /user/get/login
+Cookie: xxx</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回错误</t>
+          <t>code=0, 含 userAvatar</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1342,48 +1331,48 @@
       </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="80" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-MC-001</t>
+          <t>TC-GC-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>/微信菜单</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>创建菜单_正常</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>获取当前用户_未登录</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>POST /wx/mp/menu/create menu={button:[...]}</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1395,48 +1384,49 @@
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="80" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-MC-002</t>
+          <t>TC-GC-003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>/微信菜单</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>创建菜单_空body</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>获取当前用户_Cookie过期</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>过期 Cookie</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>body={}</t>
+          <t>GET /user/get/login
+Cookie: 过期的JWT</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1448,43 +1438,44 @@
       </c>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="80" customHeight="1">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-MC-003</t>
+          <t>TC-GC-004</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>/微信菜单</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>创建菜单_未登录</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>获取当前用户_Cookie伪造</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>伪造 Cookie</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>POST /wx/mp/menu/create</t>
+          <t>GET /user/get/login
+Cookie: userId=999999 的伪造Cookie</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1501,48 +1492,48 @@
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="80" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-WP-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>上传_50并发1MB</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>/wx/mp/portal</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>公众号门户_签名验证</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>JMeter</t>
+          <t>微信服务器GET</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50线程 POST /file/upload</t>
+          <t>GET /wx/mp/portal?signature=xxx&amp;timestamp=xxx&amp;nonce=xxx&amp;echostr=xxx</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>P95&lt;2s</t>
+          <t>返回 echostr 明文</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1554,48 +1545,49 @@
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="80" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-WP-002</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>头像_100并发</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>/wx/mp/portal</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>公众号门户_消息处理</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>JMeter</t>
+          <t>微信服务器POST</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>100线程 POST /file/upload/avatar</t>
+          <t>POST /wx/mp/portal
+Body: &lt;xml&gt;...&lt;/xml&gt;</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>P95&lt;3s</t>
+          <t>code=0, 响应XML</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1607,48 +1599,49 @@
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="80" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-WM-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>上传_缺multipart边界</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>/wx/mp/menu/create</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>创建公众号菜单</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>不完整multipart</t>
+          <t>POST /wx/mp/menu/create
+Body: {"button":[{"name":"测试","type":"click","key":"test"}]}</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>400/415</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1660,43 +1653,44 @@
       </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="80" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-WM-002</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>/文件上传</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>上传_伪PHP木马</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/wx/mp/menu/create</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>创建菜单_无菜单数据</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>file=1.jpg内容为&lt;?php...?&gt;</t>
+          <t>POST /wx/mp/menu/create
+Body: {}</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1713,48 +1707,49 @@
       </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
-    <row r="24" ht="80" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-002</t>
+          <t>TC-WM-003</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/wx/mp/menu/create</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>头像_双扩展名绕过</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>创建菜单_未登录</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>file=1.jpg.php</t>
+          <t>POST /wx/mp/menu/create
+Body: {...}</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1766,48 +1761,49 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="80" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-003</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>/头像上传</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>头像_越权修改别人</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>文件上传_50并发</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>testuser02</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>POST /file/upload/avatar userId=别人</t>
+          <t>POST /file/upload 50线程 5s内启动
+Body: multipart file=1MB_jpg</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>只改本人</t>
+          <t>P95 &lt; 2s, 错误率 &lt; 5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1819,86 +1815,60 @@
       </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
-  </sheetData>
-  <autoFilter ref="A1:M25"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>测试类型</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>用例数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>/file/upload</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>24</v>
-      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>upload_缺multipart边界</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>testuser01 Cookie</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>POST /file/upload
+Header: Content-Type: multipart/form-data (缺 boundary)
+Body: raw 乱码</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>400 或 415</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>林景彬</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/林景彬_脚本与截图/软件测试测试用例.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/file/test/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/file/upload/avatar</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/file/upload/avatar</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/file/upload/avatar</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>/file/upload/avatar</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>/file/upload/avatar</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>/wx/mp/portal</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/wx/mp/portal</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/wx/mp/menu/create</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/wx/mp/menu/create</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/wx/mp/menu/create</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/file/upload</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
